--- a/data/trans_orig/P64B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P64B-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de jornada que tiene en su trabajo en 2007</t>
+          <t>Población según el tipo de jornada que tiene en su trabajo en 2007 (tasa de respuesta: 98,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18536</t>
+          <t>18246</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38250</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18842</t>
+          <t>18303</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26055</t>
+          <t>26708</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49990</t>
+          <t>51640</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49905</t>
+          <t>50322</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80628</t>
+          <t>79361</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11319</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27709</t>
+          <t>26855</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65245</t>
+          <t>65704</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98669</t>
+          <t>99325</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12921</t>
+          <t>13725</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7924</t>
+          <t>8958</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17954</t>
+          <t>17598</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6854</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4596</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18407</t>
+          <t>18040</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6471</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21421</t>
+          <t>22157</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>94236</t>
+          <t>92771</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>131429</t>
+          <t>129042</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45266</t>
+          <t>45781</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>69961</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>148697</t>
+          <t>147804</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>191320</t>
+          <t>191881</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,06%</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>136254</t>
+          <t>135656</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>174374</t>
+          <t>175799</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42292</t>
+          <t>42458</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>65856</t>
+          <t>65625</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>184486</t>
+          <t>186416</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>231390</t>
+          <t>231614</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,73%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45193</t>
+          <t>47419</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76713</t>
+          <t>76584</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21240</t>
+          <t>20578</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44362</t>
+          <t>44803</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76133</t>
+          <t>75227</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113067</t>
+          <t>115166</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>202434</t>
+          <t>202404</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>256805</t>
+          <t>255859</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>102257</t>
+          <t>103298</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>143424</t>
+          <t>143832</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>317473</t>
+          <t>317276</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>387876</t>
+          <t>383244</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>19233</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42453</t>
+          <t>41462</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10727</t>
+          <t>10995</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24058</t>
+          <t>23706</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48316</t>
+          <t>50167</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>16395</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36784</t>
+          <t>37672</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24317</t>
+          <t>24269</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47197</t>
+          <t>48265</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45907</t>
+          <t>44986</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>76326</t>
+          <t>77123</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>210449</t>
+          <t>210087</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>266485</t>
+          <t>265531</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>147760</t>
+          <t>144879</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>191042</t>
+          <t>190621</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>372198</t>
+          <t>370630</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>442263</t>
+          <t>440817</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>495769</t>
+          <t>494519</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>562578</t>
+          <t>561464</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>184111</t>
+          <t>184483</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>231220</t>
+          <t>232056</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>690195</t>
+          <t>689850</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>773021</t>
+          <t>774281</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,16%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17835</t>
+          <t>19313</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40251</t>
+          <t>41303</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16259</t>
+          <t>16046</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25328</t>
+          <t>26440</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>50955</t>
+          <t>50658</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32433</t>
+          <t>32027</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>57413</t>
+          <t>57811</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42470</t>
+          <t>42850</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68324</t>
+          <t>70114</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>81210</t>
+          <t>79070</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>120271</t>
+          <t>117622</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12830</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2427</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15533</t>
+          <t>14338</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17169</t>
+          <t>17677</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23624</t>
+          <t>23133</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15886</t>
+          <t>15932</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36503</t>
+          <t>35330</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>143997</t>
+          <t>144199</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>183430</t>
+          <t>184140</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>113518</t>
+          <t>112532</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>147646</t>
+          <t>146076</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>266164</t>
+          <t>266320</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>319946</t>
+          <t>319182</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,46%</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>134028</t>
+          <t>134031</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>174927</t>
+          <t>172431</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59919</t>
+          <t>59186</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>89216</t>
+          <t>87313</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>202376</t>
+          <t>203257</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>253466</t>
+          <t>253272</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>94877</t>
+          <t>95834</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>138106</t>
+          <t>136578</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37234</t>
+          <t>36087</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>66088</t>
+          <t>66480</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>142445</t>
+          <t>143924</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>195649</t>
+          <t>195175</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>306943</t>
+          <t>302648</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>373350</t>
+          <t>372848</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>169200</t>
+          <t>172749</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>220875</t>
+          <t>220258</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>487927</t>
+          <t>489913</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>576142</t>
+          <t>576143</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25555</t>
+          <t>26799</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>51988</t>
+          <t>52410</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>6458</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>21664</t>
+          <t>21824</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>36195</t>
+          <t>36718</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>65108</t>
+          <t>68011</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -3456,12 +3456,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25240</t>
+          <t>25308</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>50645</t>
+          <t>49280</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>44267</t>
+          <t>45014</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>74021</t>
+          <t>74544</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>77814</t>
+          <t>78032</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>114667</t>
+          <t>115829</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>473466</t>
+          <t>471677</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>549898</t>
+          <t>551550</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>327702</t>
+          <t>327297</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>387033</t>
+          <t>392476</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>816613</t>
+          <t>817992</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>914880</t>
+          <t>922726</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -3682,12 +3682,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>796302</t>
+          <t>789797</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>879524</t>
+          <t>879145</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>305948</t>
+          <t>302321</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>365369</t>
+          <t>364824</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1118623</t>
+          <t>1118914</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1225943</t>
+          <t>1223211</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,44%</t>
         </is>
       </c>
     </row>
@@ -3948,7 +3948,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de jornada que tiene en su trabajo en 2012</t>
+          <t>Población según el tipo de jornada que tiene en su trabajo en 2012 (tasa de respuesta: 97,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23317</t>
+          <t>23629</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12837</t>
+          <t>12412</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30995</t>
+          <t>30044</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24333</t>
+          <t>23727</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46065</t>
+          <t>47591</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>15,02%</t>
         </is>
       </c>
     </row>
@@ -4256,12 +4256,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16849</t>
+          <t>16600</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36186</t>
+          <t>35660</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8958</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25208</t>
+          <t>25739</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>29568</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53224</t>
+          <t>53584</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -4369,12 +4369,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15260</t>
+          <t>15647</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3822</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14801</t>
+          <t>16531</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16491</t>
+          <t>16521</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4532,12 +4532,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>5333</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17858</t>
+          <t>18499</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4567,12 +4567,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -4595,12 +4595,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42537</t>
+          <t>43405</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67443</t>
+          <t>68943</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4610,12 +4610,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34585</t>
+          <t>35643</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57581</t>
+          <t>57857</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>84083</t>
+          <t>86347</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119015</t>
+          <t>119831</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -4708,12 +4708,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61957</t>
+          <t>61851</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88964</t>
+          <t>89323</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4723,12 +4723,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36868</t>
+          <t>37300</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59916</t>
+          <t>60944</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4758,12 +4758,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>104719</t>
+          <t>103466</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>141099</t>
+          <t>138971</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>43,85%</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30285</t>
+          <t>30548</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56018</t>
+          <t>58148</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23353</t>
+          <t>22750</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46099</t>
+          <t>46984</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4988,47 +4988,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>8,26%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>76085</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>60209</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>97114</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>4,11%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>8,11%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>76085</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>59996</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>94297</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>223970</t>
+          <t>224626</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>279459</t>
+          <t>280006</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75858</t>
+          <t>74156</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>114594</t>
+          <t>109835</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>309372</t>
+          <t>311368</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>376952</t>
+          <t>380477</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -5164,12 +5164,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20274</t>
+          <t>19445</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42031</t>
+          <t>44240</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15302</t>
+          <t>15265</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5214,12 +5214,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26642</t>
+          <t>25726</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52656</t>
+          <t>51298</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -5277,12 +5277,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9751</t>
+          <t>9238</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25380</t>
+          <t>25220</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5292,12 +5292,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33924</t>
+          <t>33220</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61156</t>
+          <t>60338</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48057</t>
+          <t>46954</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>79298</t>
+          <t>80731</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -5390,12 +5390,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>173950</t>
+          <t>174657</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>223508</t>
+          <t>224081</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5405,12 +5405,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>169329</t>
+          <t>171847</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>218370</t>
+          <t>217614</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>359474</t>
+          <t>359044</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>424303</t>
+          <t>427242</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -5503,12 +5503,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>331105</t>
+          <t>329920</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>390379</t>
+          <t>391769</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>174909</t>
+          <t>174408</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>222368</t>
+          <t>221364</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>521705</t>
+          <t>520902</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>596207</t>
+          <t>594625</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,57%</t>
         </is>
       </c>
     </row>
@@ -5733,12 +5733,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13268</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34514</t>
+          <t>33977</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5748,12 +5748,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23422</t>
+          <t>22576</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>23928</t>
+          <t>23154</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48913</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -5846,12 +5846,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42728</t>
+          <t>44207</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71679</t>
+          <t>75311</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30448</t>
+          <t>29189</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56372</t>
+          <t>55645</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80392</t>
+          <t>80817</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>120806</t>
+          <t>120484</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -5959,12 +5959,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15874</t>
+          <t>16059</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5974,12 +5974,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5994,12 +5994,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>970</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6009,12 +6009,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4969</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20235</t>
+          <t>20385</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -6072,12 +6072,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20661</t>
+          <t>20248</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24602</t>
+          <t>23868</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6142,12 +6142,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>14912</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>37600</t>
+          <t>38391</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -6185,12 +6185,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>100165</t>
+          <t>100553</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>134352</t>
+          <t>136084</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6220,12 +6220,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>92025</t>
+          <t>93086</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>124188</t>
+          <t>125580</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>201811</t>
+          <t>203064</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>251462</t>
+          <t>252154</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,5%</t>
         </is>
       </c>
     </row>
@@ -6298,12 +6298,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>82651</t>
+          <t>80458</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>115424</t>
+          <t>115095</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6333,12 +6333,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>39205</t>
+          <t>37521</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>65159</t>
+          <t>64959</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6348,12 +6348,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>128313</t>
+          <t>127772</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>170554</t>
+          <t>171841</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -6528,12 +6528,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>59806</t>
+          <t>59960</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96868</t>
+          <t>99010</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>50307</t>
+          <t>51726</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>83347</t>
+          <t>84067</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6598,12 +6598,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>119033</t>
+          <t>120287</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>169706</t>
+          <t>169579</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -6641,12 +6641,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>300876</t>
+          <t>301709</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>366541</t>
+          <t>366850</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6676,12 +6676,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>126631</t>
+          <t>126703</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>174939</t>
+          <t>174164</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6711,12 +6711,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>441949</t>
+          <t>443478</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>525361</t>
+          <t>524283</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -6754,12 +6754,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>31463</t>
+          <t>31909</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>58817</t>
+          <t>59744</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6789,12 +6789,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>20540</t>
+          <t>20856</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6824,12 +6824,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>42563</t>
+          <t>40762</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>75024</t>
+          <t>73369</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18703</t>
+          <t>18689</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>40630</t>
+          <t>41700</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>54717</t>
+          <t>52793</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>89221</t>
+          <t>87224</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>76868</t>
+          <t>78943</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>117496</t>
+          <t>117713</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -6980,12 +6980,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>340513</t>
+          <t>339276</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>405592</t>
+          <t>410276</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6995,12 +6995,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>318580</t>
+          <t>316406</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>381902</t>
+          <t>377418</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>675227</t>
+          <t>674852</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>766119</t>
+          <t>767727</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,02%</t>
         </is>
       </c>
     </row>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>498059</t>
+          <t>495676</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>571480</t>
+          <t>569497</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7108,12 +7108,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>265943</t>
+          <t>268624</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>325899</t>
+          <t>322844</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7143,12 +7143,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>780593</t>
+          <t>782858</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>875310</t>
+          <t>874975</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,63%</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de jornada que tiene en su trabajo en 2016</t>
+          <t>Población según el tipo de jornada que tiene en su trabajo en 2016 (tasa de respuesta: 94,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23486</t>
+          <t>23916</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19540</t>
+          <t>19080</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17963</t>
+          <t>18473</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36846</t>
+          <t>38304</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -7667,12 +7667,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12982</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31156</t>
+          <t>31340</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7682,12 +7682,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11428</t>
+          <t>10686</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17072</t>
+          <t>17933</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38565</t>
+          <t>39869</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7815,62 +7815,62 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>1884</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>6755</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1884</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>6463</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -7893,12 +7893,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7928,12 +7928,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11614</t>
+          <t>11937</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7963,12 +7963,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2271</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11914</t>
+          <t>11334</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -8006,12 +8006,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29369</t>
+          <t>28491</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50235</t>
+          <t>49662</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8021,12 +8021,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8041,12 +8041,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14007</t>
+          <t>14525</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28670</t>
+          <t>29474</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46770</t>
+          <t>47009</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>74606</t>
+          <t>72748</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,07%</t>
         </is>
       </c>
     </row>
@@ -8119,12 +8119,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42643</t>
+          <t>43921</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65700</t>
+          <t>66480</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8154,12 +8154,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13862</t>
+          <t>13362</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28278</t>
+          <t>28578</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>61607</t>
+          <t>61801</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>89316</t>
+          <t>89929</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,83%</t>
         </is>
       </c>
     </row>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76415</t>
+          <t>75572</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>116053</t>
+          <t>114378</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8364,12 +8364,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8384,12 +8384,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62390</t>
+          <t>62457</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96972</t>
+          <t>96379</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8419,12 +8419,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>144799</t>
+          <t>147112</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>194732</t>
+          <t>197577</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -8462,12 +8462,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>159003</t>
+          <t>159273</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>209099</t>
+          <t>210287</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>91812</t>
+          <t>93192</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>130323</t>
+          <t>130035</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>265280</t>
+          <t>264018</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>328559</t>
+          <t>325593</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11363</t>
+          <t>12177</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31693</t>
+          <t>31089</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8610,12 +8610,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12468</t>
+          <t>12195</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17657</t>
+          <t>16869</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38389</t>
+          <t>38327</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -8688,12 +8688,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15042</t>
+          <t>14612</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34013</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8703,12 +8703,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34011</t>
+          <t>33423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59291</t>
+          <t>61610</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53835</t>
+          <t>53448</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>87517</t>
+          <t>85885</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -8801,12 +8801,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>170268</t>
+          <t>172386</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>220897</t>
+          <t>221352</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8816,12 +8816,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>154198</t>
+          <t>153942</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>196541</t>
+          <t>198334</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8851,12 +8851,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8871,12 +8871,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>334476</t>
+          <t>334167</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>404831</t>
+          <t>400012</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8886,12 +8886,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -8914,12 +8914,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>333039</t>
+          <t>334086</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>394441</t>
+          <t>395616</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8929,12 +8929,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>184955</t>
+          <t>183051</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>231977</t>
+          <t>231392</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8984,12 +8984,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>534975</t>
+          <t>533471</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>613296</t>
+          <t>611214</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8999,12 +8999,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,73%</t>
         </is>
       </c>
     </row>
@@ -9144,12 +9144,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26603</t>
+          <t>28559</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53623</t>
+          <t>56181</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9159,12 +9159,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20631</t>
+          <t>20549</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42201</t>
+          <t>44137</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>52288</t>
+          <t>53398</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>86970</t>
+          <t>88040</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -9257,12 +9257,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35057</t>
+          <t>34150</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62247</t>
+          <t>60678</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9272,12 +9272,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33023</t>
+          <t>33414</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58471</t>
+          <t>58692</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9307,12 +9307,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73846</t>
+          <t>74699</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>109234</t>
+          <t>111010</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9342,12 +9342,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -9370,12 +9370,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9288</t>
+          <t>9298</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9385,82 +9385,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1048</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5303</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>5030</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>10637</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1048</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>5281</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>5030</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>1942</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>11268</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -9483,12 +9483,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15023</t>
+          <t>14645</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>13803</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32134</t>
+          <t>32486</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9533,12 +9533,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20500</t>
+          <t>20724</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>43389</t>
+          <t>42603</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -9596,12 +9596,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>128210</t>
+          <t>127483</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>165465</t>
+          <t>165938</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>118834</t>
+          <t>120399</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>155006</t>
+          <t>156517</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9646,12 +9646,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>258721</t>
+          <t>261597</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>310636</t>
+          <t>309717</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9681,12 +9681,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,4%</t>
         </is>
       </c>
     </row>
@@ -9709,12 +9709,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>79451</t>
+          <t>78035</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>112562</t>
+          <t>112890</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>51765</t>
+          <t>51013</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>81405</t>
+          <t>78824</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9759,12 +9759,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>140146</t>
+          <t>140426</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>183772</t>
+          <t>183587</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -9939,12 +9939,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>125781</t>
+          <t>124728</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>174597</t>
+          <t>173920</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9974,12 +9974,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>99862</t>
+          <t>99295</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>142478</t>
+          <t>140994</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9989,12 +9989,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>237209</t>
+          <t>233476</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>301064</t>
+          <t>295823</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10024,12 +10024,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -10052,12 +10052,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>220496</t>
+          <t>220734</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>281415</t>
+          <t>279142</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10087,12 +10087,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>138813</t>
+          <t>141962</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>186557</t>
+          <t>186465</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>373495</t>
+          <t>374709</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>451562</t>
+          <t>449223</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -10165,12 +10165,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17103</t>
+          <t>16811</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>38352</t>
+          <t>37594</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10200,12 +10200,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>14681</t>
+          <t>15404</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10215,12 +10215,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10235,12 +10235,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>23219</t>
+          <t>23620</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>46566</t>
+          <t>47146</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -10278,12 +10278,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21815</t>
+          <t>21796</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46040</t>
+          <t>44489</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10293,12 +10293,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10313,12 +10313,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>58033</t>
+          <t>56511</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>90843</t>
+          <t>90911</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -10348,12 +10348,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>85167</t>
+          <t>87029</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>127207</t>
+          <t>127641</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10363,12 +10363,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>349659</t>
+          <t>346359</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>415967</t>
+          <t>413749</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>303063</t>
+          <t>300631</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>364651</t>
+          <t>362042</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>665725</t>
+          <t>669799</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>758051</t>
+          <t>763504</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10476,12 +10476,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -10504,12 +10504,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>478953</t>
+          <t>478852</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>552714</t>
+          <t>551878</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>266278</t>
+          <t>264379</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>324071</t>
+          <t>322552</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10574,12 +10574,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>765179</t>
+          <t>758917</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>858840</t>
+          <t>852718</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10589,12 +10589,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P64B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P64B-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18246</t>
+          <t>17947</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>39711</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18303</t>
+          <t>18969</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26708</t>
+          <t>26370</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51640</t>
+          <t>50871</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50322</t>
+          <t>50218</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79361</t>
+          <t>80500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26855</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65704</t>
+          <t>64588</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99325</t>
+          <t>99974</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13725</t>
+          <t>13429</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8958</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17598</t>
+          <t>17350</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18040</t>
+          <t>18640</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6471</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22157</t>
+          <t>21616</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92771</t>
+          <t>93837</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>129042</t>
+          <t>128702</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45781</t>
+          <t>44868</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>69718</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>147804</t>
+          <t>149595</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>191881</t>
+          <t>192955</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,27%</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>135656</t>
+          <t>135897</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>175799</t>
+          <t>173980</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42458</t>
+          <t>41956</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>65625</t>
+          <t>66479</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>186416</t>
+          <t>187064</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>231614</t>
+          <t>233384</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>45,07%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47419</t>
+          <t>47023</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76584</t>
+          <t>77054</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20578</t>
+          <t>22911</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44803</t>
+          <t>45788</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75227</t>
+          <t>75980</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115166</t>
+          <t>113200</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>202404</t>
+          <t>201650</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>255859</t>
+          <t>258375</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>103298</t>
+          <t>102928</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>143832</t>
+          <t>144083</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>317276</t>
+          <t>318740</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>383244</t>
+          <t>384598</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19233</t>
+          <t>18023</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41462</t>
+          <t>41499</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1767</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10995</t>
+          <t>11342</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23706</t>
+          <t>22776</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50167</t>
+          <t>47638</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16395</t>
+          <t>16892</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37672</t>
+          <t>38383</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24269</t>
+          <t>23423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48265</t>
+          <t>46386</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44986</t>
+          <t>44602</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>77123</t>
+          <t>75037</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>210087</t>
+          <t>210566</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>265531</t>
+          <t>266928</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>144879</t>
+          <t>146046</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>190621</t>
+          <t>188969</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>370630</t>
+          <t>372631</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>440817</t>
+          <t>443454</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>494519</t>
+          <t>494726</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>561464</t>
+          <t>566575</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>184483</t>
+          <t>185017</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>232056</t>
+          <t>229680</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>689850</t>
+          <t>693864</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>774281</t>
+          <t>775130</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,21%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19313</t>
+          <t>18684</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41303</t>
+          <t>39252</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16046</t>
+          <t>15927</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26440</t>
+          <t>25016</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>50658</t>
+          <t>50664</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32027</t>
+          <t>31945</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>57811</t>
+          <t>57546</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>42850</t>
+          <t>43291</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70114</t>
+          <t>69330</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79070</t>
+          <t>81427</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>117622</t>
+          <t>119508</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,4%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>12529</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2427</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14338</t>
+          <t>14955</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4207</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17677</t>
+          <t>17835</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8857</t>
+          <t>8864</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23133</t>
+          <t>24434</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15932</t>
+          <t>15886</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>35330</t>
+          <t>35097</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>144199</t>
+          <t>142633</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>184140</t>
+          <t>183329</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>112532</t>
+          <t>114263</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>146076</t>
+          <t>148287</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>266320</t>
+          <t>266197</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>319182</t>
+          <t>319738</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,54%</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>134031</t>
+          <t>134182</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>172431</t>
+          <t>174643</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59186</t>
+          <t>59479</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>87313</t>
+          <t>89439</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>203257</t>
+          <t>204020</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>253272</t>
+          <t>253200</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>95834</t>
+          <t>94229</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>136578</t>
+          <t>138898</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36087</t>
+          <t>36961</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>66480</t>
+          <t>69322</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>143924</t>
+          <t>141451</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>195175</t>
+          <t>194412</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>302648</t>
+          <t>303251</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>372848</t>
+          <t>367260</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>172749</t>
+          <t>172207</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>220258</t>
+          <t>224034</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>489913</t>
+          <t>487395</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>576143</t>
+          <t>572085</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>26799</t>
+          <t>25921</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>52410</t>
+          <t>51991</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>6718</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>21824</t>
+          <t>21241</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>36718</t>
+          <t>37226</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>68011</t>
+          <t>65909</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -3456,12 +3456,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25308</t>
+          <t>26566</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49280</t>
+          <t>50994</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>45014</t>
+          <t>45585</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>74544</t>
+          <t>75047</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>78032</t>
+          <t>77549</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>115829</t>
+          <t>118041</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>471677</t>
+          <t>472391</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>551550</t>
+          <t>552222</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>327297</t>
+          <t>325894</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>392476</t>
+          <t>386996</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>817992</t>
+          <t>818615</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>922726</t>
+          <t>925255</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -3682,12 +3682,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>789797</t>
+          <t>791207</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>879145</t>
+          <t>879699</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>302321</t>
+          <t>303123</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>364824</t>
+          <t>363157</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1118914</t>
+          <t>1117450</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1223211</t>
+          <t>1224374</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,48%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23629</t>
+          <t>23214</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12412</t>
+          <t>12456</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30044</t>
+          <t>29722</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23727</t>
+          <t>23789</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47591</t>
+          <t>46591</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -4256,12 +4256,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16600</t>
+          <t>16647</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35660</t>
+          <t>35406</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9116</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25739</t>
+          <t>25059</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29568</t>
+          <t>29621</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53584</t>
+          <t>54613</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -4369,12 +4369,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15647</t>
+          <t>15251</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>15467</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16521</t>
+          <t>15746</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4532,12 +4532,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18499</t>
+          <t>18733</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4567,12 +4567,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -4595,12 +4595,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43405</t>
+          <t>42740</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68943</t>
+          <t>67241</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4610,12 +4610,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35643</t>
+          <t>35153</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57857</t>
+          <t>58265</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>86347</t>
+          <t>84328</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119831</t>
+          <t>118013</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,24%</t>
         </is>
       </c>
     </row>
@@ -4708,12 +4708,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61851</t>
+          <t>61973</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>89323</t>
+          <t>88704</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4723,12 +4723,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37300</t>
+          <t>36822</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60944</t>
+          <t>59133</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4758,12 +4758,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>103466</t>
+          <t>105137</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>138971</t>
+          <t>140384</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,3%</t>
         </is>
       </c>
     </row>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30548</t>
+          <t>31685</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58148</t>
+          <t>60152</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4953,12 +4953,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22750</t>
+          <t>23048</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46984</t>
+          <t>46970</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5008,12 +5008,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60209</t>
+          <t>59456</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>97114</t>
+          <t>95640</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5023,12 +5023,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -5051,12 +5051,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>224626</t>
+          <t>224388</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>280006</t>
+          <t>278515</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>74156</t>
+          <t>74597</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>109835</t>
+          <t>110762</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5101,12 +5101,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>311368</t>
+          <t>310993</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>380477</t>
+          <t>378606</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -5164,12 +5164,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19445</t>
+          <t>18978</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44240</t>
+          <t>41214</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15265</t>
+          <t>15815</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5214,12 +5214,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25726</t>
+          <t>25769</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>51298</t>
+          <t>50998</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -5277,12 +5277,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9238</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25220</t>
+          <t>26932</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5292,12 +5292,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33220</t>
+          <t>34415</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60338</t>
+          <t>61216</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46954</t>
+          <t>46528</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80731</t>
+          <t>78815</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -5390,12 +5390,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>174657</t>
+          <t>175306</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>224081</t>
+          <t>223582</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5405,12 +5405,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>171847</t>
+          <t>169750</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>217614</t>
+          <t>214045</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>359044</t>
+          <t>355850</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>427242</t>
+          <t>427149</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -5503,12 +5503,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>329920</t>
+          <t>329697</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>391769</t>
+          <t>389332</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>174408</t>
+          <t>174904</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>221364</t>
+          <t>221937</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>520902</t>
+          <t>520387</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>594625</t>
+          <t>598113</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,81%</t>
         </is>
       </c>
     </row>
@@ -5733,12 +5733,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12454</t>
+          <t>12456</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33977</t>
+          <t>32634</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7035</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22576</t>
+          <t>24024</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>23154</t>
+          <t>22752</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>50492</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -5846,12 +5846,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44207</t>
+          <t>43199</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>75311</t>
+          <t>73044</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29189</t>
+          <t>29287</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55645</t>
+          <t>54196</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80817</t>
+          <t>79587</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>120484</t>
+          <t>120358</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -5959,12 +5959,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16059</t>
+          <t>15093</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5974,12 +5974,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5994,12 +5994,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>985</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>11683</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6009,12 +6009,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20385</t>
+          <t>21278</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -6072,12 +6072,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20248</t>
+          <t>20100</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23868</t>
+          <t>22886</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6142,12 +6142,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>14562</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38391</t>
+          <t>38634</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -6185,12 +6185,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>100553</t>
+          <t>100765</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>136084</t>
+          <t>138244</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6220,12 +6220,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>93086</t>
+          <t>92718</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>125580</t>
+          <t>125849</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>203064</t>
+          <t>201309</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>252154</t>
+          <t>253049</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,66%</t>
         </is>
       </c>
     </row>
@@ -6298,12 +6298,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>80458</t>
+          <t>81730</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>115095</t>
+          <t>117272</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6333,12 +6333,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37521</t>
+          <t>38032</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>64959</t>
+          <t>63679</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6348,12 +6348,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>127772</t>
+          <t>126834</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>171841</t>
+          <t>171139</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -6528,12 +6528,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>59960</t>
+          <t>59672</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>99010</t>
+          <t>97336</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>51726</t>
+          <t>51092</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>84067</t>
+          <t>84541</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6598,12 +6598,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>120287</t>
+          <t>121980</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>169579</t>
+          <t>169809</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -6641,12 +6641,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>301709</t>
+          <t>297741</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>366850</t>
+          <t>364777</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6676,12 +6676,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>126703</t>
+          <t>125829</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>174164</t>
+          <t>173694</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6711,12 +6711,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>443478</t>
+          <t>442715</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>524283</t>
+          <t>525152</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -6754,12 +6754,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>31909</t>
+          <t>33366</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>59744</t>
+          <t>60812</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6789,12 +6789,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>20856</t>
+          <t>20340</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6824,12 +6824,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>40762</t>
+          <t>42626</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>73369</t>
+          <t>71741</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18689</t>
+          <t>18195</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>41700</t>
+          <t>40205</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6882,12 +6882,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>52793</t>
+          <t>53006</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>87224</t>
+          <t>87926</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>78943</t>
+          <t>78078</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>117713</t>
+          <t>119491</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -6980,12 +6980,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>339276</t>
+          <t>336616</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>410276</t>
+          <t>405342</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6995,12 +6995,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>316406</t>
+          <t>316868</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>377418</t>
+          <t>375727</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>674852</t>
+          <t>677407</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>767727</t>
+          <t>770209</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>495676</t>
+          <t>493173</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>569497</t>
+          <t>567129</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7108,12 +7108,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>268624</t>
+          <t>267434</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>322844</t>
+          <t>325462</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7143,12 +7143,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>782858</t>
+          <t>778669</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>874975</t>
+          <t>877425</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,74%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23916</t>
+          <t>23748</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19080</t>
+          <t>19256</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18473</t>
+          <t>17234</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38304</t>
+          <t>38249</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -7667,12 +7667,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>13307</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31340</t>
+          <t>32343</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7682,12 +7682,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>11610</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17933</t>
+          <t>18073</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39869</t>
+          <t>38180</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6321</t>
+          <t>6650</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -7928,12 +7928,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>11953</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7963,12 +7963,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11334</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -8006,12 +8006,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28491</t>
+          <t>27618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49662</t>
+          <t>49500</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8021,12 +8021,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8041,12 +8041,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14525</t>
+          <t>14697</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29474</t>
+          <t>29042</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47009</t>
+          <t>46900</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72748</t>
+          <t>73628</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,52%</t>
         </is>
       </c>
     </row>
@@ -8119,12 +8119,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43921</t>
+          <t>44199</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66480</t>
+          <t>67788</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8154,12 +8154,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13362</t>
+          <t>13339</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28578</t>
+          <t>28457</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>61801</t>
+          <t>62319</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>89929</t>
+          <t>90650</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>46,19%</t>
         </is>
       </c>
     </row>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75572</t>
+          <t>77168</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114378</t>
+          <t>115874</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8364,12 +8364,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8384,12 +8384,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>62457</t>
+          <t>61875</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96379</t>
+          <t>95389</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8419,12 +8419,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>147112</t>
+          <t>147396</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>197577</t>
+          <t>196601</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -8462,12 +8462,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>159273</t>
+          <t>161162</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>210287</t>
+          <t>208542</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>93192</t>
+          <t>91389</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>130035</t>
+          <t>131307</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>264018</t>
+          <t>265751</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>325593</t>
+          <t>327575</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12177</t>
+          <t>12168</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31089</t>
+          <t>31683</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8610,12 +8610,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>12594</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16869</t>
+          <t>17564</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38327</t>
+          <t>39361</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -8688,12 +8688,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14612</t>
+          <t>14493</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34137</t>
+          <t>34612</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8703,12 +8703,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33423</t>
+          <t>33991</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61610</t>
+          <t>61332</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53448</t>
+          <t>52142</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>85885</t>
+          <t>86051</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -8801,12 +8801,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>172386</t>
+          <t>170865</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>221352</t>
+          <t>221679</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8816,12 +8816,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>153942</t>
+          <t>153300</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>198334</t>
+          <t>197156</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8851,12 +8851,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8871,12 +8871,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>334167</t>
+          <t>338270</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>400012</t>
+          <t>404169</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8886,12 +8886,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -8914,12 +8914,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>334086</t>
+          <t>333573</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>395616</t>
+          <t>394492</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8929,12 +8929,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>183051</t>
+          <t>184433</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>231392</t>
+          <t>231124</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8984,12 +8984,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>533471</t>
+          <t>532276</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>611214</t>
+          <t>609084</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8999,12 +8999,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,59%</t>
         </is>
       </c>
     </row>
@@ -9144,12 +9144,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28559</t>
+          <t>27808</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56181</t>
+          <t>53448</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9159,12 +9159,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20549</t>
+          <t>19911</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44137</t>
+          <t>41493</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>53398</t>
+          <t>53704</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>88040</t>
+          <t>88620</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -9257,12 +9257,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34150</t>
+          <t>34585</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>60678</t>
+          <t>61287</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9272,12 +9272,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33414</t>
+          <t>34798</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58692</t>
+          <t>58736</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9307,12 +9307,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74699</t>
+          <t>73620</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>111010</t>
+          <t>109832</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9342,12 +9342,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -9370,12 +9370,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9298</t>
+          <t>9973</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9385,12 +9385,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9440,12 +9440,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1740</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>10740</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9455,12 +9455,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -9483,12 +9483,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14645</t>
+          <t>15778</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9518,12 +9518,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13803</t>
+          <t>13920</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32486</t>
+          <t>33039</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9533,12 +9533,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20724</t>
+          <t>20931</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>42603</t>
+          <t>43384</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -9596,12 +9596,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>127483</t>
+          <t>127982</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>165938</t>
+          <t>166017</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9631,12 +9631,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>120399</t>
+          <t>120673</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>156517</t>
+          <t>154978</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9646,12 +9646,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>261597</t>
+          <t>260194</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>309717</t>
+          <t>308707</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9681,12 +9681,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,25%</t>
         </is>
       </c>
     </row>
@@ -9709,12 +9709,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>78035</t>
+          <t>77271</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>112890</t>
+          <t>112446</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>51013</t>
+          <t>52261</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>78824</t>
+          <t>79374</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9759,12 +9759,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>140426</t>
+          <t>140561</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>183587</t>
+          <t>184041</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -9939,12 +9939,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>124728</t>
+          <t>125530</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>173920</t>
+          <t>170212</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9974,12 +9974,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>99295</t>
+          <t>98929</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>140994</t>
+          <t>140798</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9989,12 +9989,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>233476</t>
+          <t>232891</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>295823</t>
+          <t>294907</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10024,12 +10024,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -10052,12 +10052,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>220734</t>
+          <t>223388</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>279142</t>
+          <t>279493</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10087,12 +10087,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>141962</t>
+          <t>139481</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>186465</t>
+          <t>188409</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10102,12 +10102,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10122,12 +10122,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>374709</t>
+          <t>378611</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>449223</t>
+          <t>454792</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -10165,12 +10165,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16811</t>
+          <t>16633</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>37594</t>
+          <t>37759</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10200,12 +10200,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>15404</t>
+          <t>13783</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10215,12 +10215,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10235,12 +10235,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>23620</t>
+          <t>23112</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>47146</t>
+          <t>46524</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -10278,12 +10278,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21796</t>
+          <t>21656</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>44489</t>
+          <t>44331</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10293,12 +10293,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10313,12 +10313,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>56511</t>
+          <t>57749</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>90911</t>
+          <t>92357</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10328,12 +10328,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10348,12 +10348,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>87029</t>
+          <t>86854</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>127641</t>
+          <t>127613</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>346359</t>
+          <t>344394</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>413749</t>
+          <t>414054</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>300631</t>
+          <t>304887</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>362042</t>
+          <t>363690</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>669799</t>
+          <t>667481</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>763504</t>
+          <t>760437</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10476,12 +10476,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -10504,12 +10504,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>478852</t>
+          <t>477678</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>551878</t>
+          <t>552235</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>264379</t>
+          <t>263528</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>322552</t>
+          <t>319972</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10574,12 +10574,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>758917</t>
+          <t>762967</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>852718</t>
+          <t>853687</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10589,12 +10589,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
